--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,9 +81,16 @@
     <t>Description</t>
   </si>
   <si>
-    <t>314e profile of the FHIR Timing datatype.
-Uses 314e date/time related datatypes
-including DateTime314e, Period314e, and Quantity314e.</t>
+    <t>Describes the occurrence of an event that may occur multiple times. Timing schedules are used 
+for specifying when events are expected or requested to occur and may also be used to represent 
+the summary of a past or ongoing event. For simplicity, the definitions of Timing components 
+are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
+A Timing schedule can be a list of events and/or criteria for when the event happens, which can 
+be expressed in a structured form and/or as a code. When both event and a repeating specification 
+are provided, the list of events should be understood as an interpretation of the information in the repeat structure.
+Note: The Timing data type allows modifier extensions.
+314e profile of the FHIR Timing datatype uses 314e datatype profiles 
+including DateTime314e, Period314e, CodeableConcept314e and Quantity314e.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -361,7 +368,7 @@
 </t>
   </si>
   <si>
-    <t>Scheduled event time in UTC</t>
+    <t>When the event occurs, in UTC</t>
   </si>
   <si>
     <t>Identifies specific times when the event occurs.</t>
@@ -452,7 +459,7 @@
     <t>Timing.repeat.duration</t>
   </si>
   <si>
-    <t xml:space="preserve">decimal
+    <t xml:space="preserve">decimal {http://314e.com/fhir/ig/StructureDefinition/decimal-314e}
 </t>
   </si>
   <si>
@@ -565,7 +572,7 @@
     <t>Timing.repeat.timeOfDay</t>
   </si>
   <si>
-    <t xml:space="preserve">time
+    <t xml:space="preserve">time {http://314e.com/fhir/ig/StructureDefinition/time-314e}
 </t>
   </si>
   <si>
@@ -609,7 +616,7 @@
 </t>
   </si>
   <si>
-    <t>Minutes from event with standard FHIR semantics</t>
+    <t>Minutes from event (before or after)</t>
   </si>
   <si>
     <t>The number of minutes from the event. If the event code does not indicate whether the minutes is before or after the event, then the offset is assumed to be after the event.</t>
@@ -621,7 +628,7 @@
     <t>Timing.code</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-timing-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-timing-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
